--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -15593,11 +15593,14 @@
       <c r="C894" t="str">
         <v>Profissões e Processos</v>
       </c>
-      <c r="D894" t="b">
-        <v>0</v>
+      <c r="D894" t="str">
+        <v>publicado</v>
       </c>
       <c r="E894" t="str">
-        <v/>
+        <v>29/06/2026</v>
+      </c>
+      <c r="F894" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=-4ZD4x8EI4o | Short: https://www.youtube.com/watch?v=9vsWuAkj5ac</v>
       </c>
     </row>
     <row r="895">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -7141,11 +7141,14 @@
       <c r="C397" t="str">
         <v>Alimentação</v>
       </c>
-      <c r="D397" t="b">
-        <v>0</v>
+      <c r="D397" t="str">
+        <v>publicado</v>
       </c>
       <c r="E397" t="str">
-        <v/>
+        <v>29/06/2026</v>
+      </c>
+      <c r="F397" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=4o0X1PRIWGs | Short: https://www.youtube.com/watch?v=8DYjqC-pjBw</v>
       </c>
     </row>
     <row r="398">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -23538,11 +23538,14 @@
       <c r="C1361" t="str">
         <v>Máquinas e Mecânica</v>
       </c>
-      <c r="D1361" t="b">
-        <v>0</v>
+      <c r="D1361" t="str">
+        <v>publicado</v>
       </c>
       <c r="E1361" t="str">
-        <v/>
+        <v>29/06/2026</v>
+      </c>
+      <c r="F1361" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=Vd6SJTbUfhY | Short: https://www.youtube.com/watch?v=uklok2AzLVc</v>
       </c>
     </row>
     <row r="1362">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -3061,11 +3061,14 @@
       <c r="C157" t="str">
         <v>Curiosidades</v>
       </c>
-      <c r="D157" t="b">
-        <v>0</v>
+      <c r="D157" t="str">
+        <v>publicado</v>
       </c>
       <c r="E157" t="str">
-        <v/>
+        <v>30/06/2026</v>
+      </c>
+      <c r="F157" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=Y5qlfBouW-0 | Short: https://www.youtube.com/watch?v=-29W9-n9nE8</v>
       </c>
     </row>
     <row r="158">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -21212,11 +21212,14 @@
       <c r="C1224" t="str">
         <v>Animais Específicos</v>
       </c>
-      <c r="D1224" t="b">
-        <v>0</v>
+      <c r="D1224" t="str">
+        <v>publicado</v>
       </c>
       <c r="E1224" t="str">
-        <v/>
+        <v>30/06/2026</v>
+      </c>
+      <c r="F1224" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=x_a2uFjsD4k | Short: https://www.youtube.com/watch?v=kb0l0CHHMcM</v>
       </c>
     </row>
     <row r="1225">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -11584,11 +11584,14 @@
       <c r="C658" t="str">
         <v>Tecnologia e Cotidiano</v>
       </c>
-      <c r="D658" t="b">
-        <v>0</v>
+      <c r="D658" t="str">
+        <v>publicado</v>
       </c>
       <c r="E658" t="str">
-        <v/>
+        <v>30/06/2026</v>
+      </c>
+      <c r="F658" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=osw0y8VY1gE | Short: https://www.youtube.com/watch?v=n4rXZRxad7E</v>
       </c>
     </row>
     <row r="659">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -16336,11 +16336,14 @@
       <c r="C937" t="str">
         <v>Profissões e Processos</v>
       </c>
-      <c r="D937" t="b">
-        <v>0</v>
+      <c r="D937" t="str">
+        <v>publicado</v>
       </c>
       <c r="E937" t="str">
-        <v/>
+        <v>01/07/2026</v>
+      </c>
+      <c r="F937" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=zsJIk3Z91gA | Short: https://www.youtube.com/watch?v=X_E8Smr3a9o</v>
       </c>
     </row>
     <row r="938">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -15979,11 +15979,14 @@
       <c r="C916" t="str">
         <v>Profissões e Processos</v>
       </c>
-      <c r="D916" t="b">
-        <v>0</v>
+      <c r="D916" t="str">
+        <v>publicado</v>
       </c>
       <c r="E916" t="str">
-        <v/>
+        <v>03/07/2026</v>
+      </c>
+      <c r="F916" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=1XRXUNHYu0E | Short: https://www.youtube.com/watch?v=6LVM6Qt4KOQ</v>
       </c>
     </row>
     <row r="917">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -19028,11 +19028,14 @@
       <c r="C1095" t="str">
         <v>Países e Culturas</v>
       </c>
-      <c r="D1095" t="b">
-        <v>0</v>
+      <c r="D1095" t="str">
+        <v>publicado</v>
       </c>
       <c r="E1095" t="str">
-        <v/>
+        <v>04/07/2026</v>
+      </c>
+      <c r="F1095" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=Nu-A9gUuORo | Short: https://www.youtube.com/watch?v=gO4DUh5m8dk</v>
       </c>
     </row>
     <row r="1096">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -15928,11 +15928,14 @@
       <c r="C913" t="str">
         <v>Profissões e Processos</v>
       </c>
-      <c r="D913" t="b">
-        <v>0</v>
+      <c r="D913" t="str">
+        <v>publicado</v>
       </c>
       <c r="E913" t="str">
-        <v/>
+        <v>05/07/2026</v>
+      </c>
+      <c r="F913" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=87Jb5gYSxHY | Short: https://www.youtube.com/watch?v=BdkNZxRDIE4</v>
       </c>
     </row>
     <row r="914">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -19901,11 +19901,14 @@
       <c r="C1146" t="str">
         <v>Países e Culturas</v>
       </c>
-      <c r="D1146" t="b">
-        <v>0</v>
+      <c r="D1146" t="str">
+        <v>publicado</v>
       </c>
       <c r="E1146" t="str">
-        <v/>
+        <v>06/07/2026</v>
+      </c>
+      <c r="F1146" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=wqBYaxCVMbE | Short: https://www.youtube.com/watch?v=jFZeVZoAQQ0</v>
       </c>
     </row>
     <row r="1147">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -20040,11 +20040,14 @@
       <c r="C1154" t="str">
         <v>Animais Específicos</v>
       </c>
-      <c r="D1154" t="b">
-        <v>0</v>
+      <c r="D1154" t="str">
+        <v>publicado</v>
       </c>
       <c r="E1154" t="str">
-        <v/>
+        <v>08/07/2026</v>
+      </c>
+      <c r="F1154" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=eTVVatXWS3U | Short: https://www.youtube.com/watch?v=WnIZ_n6rbsI</v>
       </c>
     </row>
     <row r="1155">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -10003,11 +10003,14 @@
       <c r="C565" t="str">
         <v>Educação</v>
       </c>
-      <c r="D565" t="b">
-        <v>0</v>
+      <c r="D565" t="str">
+        <v>publicado</v>
       </c>
       <c r="E565" t="str">
-        <v/>
+        <v>09/07/2026</v>
+      </c>
+      <c r="F565" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=KfVIW1T8jPA | Short: https://www.youtube.com/watch?v=T8kEDXCcGAM</v>
       </c>
     </row>
     <row r="566">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -22446,11 +22446,14 @@
       <c r="C1295" t="str">
         <v>Máquinas e Mecânica</v>
       </c>
-      <c r="D1295" t="b">
-        <v>0</v>
+      <c r="D1295" t="str">
+        <v>publicado</v>
       </c>
       <c r="E1295" t="str">
-        <v/>
+        <v>10/07/2026</v>
+      </c>
+      <c r="F1295" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=22aWldYPpuk | Short: https://www.youtube.com/watch?v=3n10mU7CU_g</v>
       </c>
     </row>
     <row r="1296">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -562,11 +562,14 @@
       <c r="C10" t="str">
         <v>Ciência</v>
       </c>
-      <c r="D10" t="b">
-        <v>0</v>
+      <c r="D10" t="str">
+        <v>publicado</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>11/07/2026</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=Ey8LG9Sh948 | Short: https://www.youtube.com/watch?v=ywJCV7I8Xw0</v>
       </c>
     </row>
     <row r="11">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -3458,11 +3458,14 @@
       <c r="C180" t="str">
         <v>Curiosidades</v>
       </c>
-      <c r="D180" t="b">
-        <v>0</v>
+      <c r="D180" t="str">
+        <v>publicado</v>
       </c>
       <c r="E180" t="str">
-        <v/>
+        <v>12/07/2026</v>
+      </c>
+      <c r="F180" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=Hw3QZbWgp-g | Short: https://www.youtube.com/watch?v=tY57OpUDMWo</v>
       </c>
     </row>
     <row r="181">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -3903,11 +3903,14 @@
       <c r="C206" t="str">
         <v>Meio Ambiente</v>
       </c>
-      <c r="D206" t="b">
-        <v>0</v>
+      <c r="D206" t="str">
+        <v>publicado</v>
       </c>
       <c r="E206" t="str">
-        <v/>
+        <v>13/07/2026</v>
+      </c>
+      <c r="F206" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=CBYT1EdLyn8 | Short: https://www.youtube.com/watch?v=FbLokT3y-H0</v>
       </c>
     </row>
     <row r="207">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -22968,11 +22968,14 @@
       <c r="C1325" t="str">
         <v>Máquinas e Mecânica</v>
       </c>
-      <c r="D1325" t="b">
-        <v>0</v>
+      <c r="D1325" t="str">
+        <v>publicado</v>
       </c>
       <c r="E1325" t="str">
-        <v/>
+        <v>14/07/2026</v>
+      </c>
+      <c r="F1325" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=1nBhJyEXrTw | Short: https://www.youtube.com/watch?v=SRnpoKJfTKc</v>
       </c>
     </row>
     <row r="1326">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -23688,11 +23688,14 @@
       <c r="C1367" t="str">
         <v>Máquinas e Mecânica</v>
       </c>
-      <c r="D1367" t="b">
-        <v>0</v>
+      <c r="D1367" t="str">
+        <v>publicado</v>
       </c>
       <c r="E1367" t="str">
-        <v/>
+        <v>15/07/2026</v>
+      </c>
+      <c r="F1367" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=Vtwm4MRd1bQ | Short: https://www.youtube.com/watch?v=Zac3NjwWZ3k</v>
       </c>
     </row>
     <row r="1368">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -12177,11 +12177,14 @@
       <c r="C692" t="str">
         <v>Tecnologia e Cotidiano</v>
       </c>
-      <c r="D692" t="b">
-        <v>0</v>
+      <c r="D692" t="str">
+        <v>publicado</v>
       </c>
       <c r="E692" t="str">
-        <v/>
+        <v>16/07/2026</v>
+      </c>
+      <c r="F692" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=EKdTlxO7470 | Short: https://www.youtube.com/watch?v=ybs2Af5JbFY</v>
       </c>
     </row>
     <row r="693">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -5096,11 +5096,14 @@
       <c r="C276" t="str">
         <v>Animais</v>
       </c>
-      <c r="D276" t="b">
-        <v>0</v>
+      <c r="D276" t="str">
+        <v>publicado</v>
       </c>
       <c r="E276" t="str">
-        <v/>
+        <v>17/07/2026</v>
+      </c>
+      <c r="F276" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=bDPpnzi3TL4 | Short: https://www.youtube.com/watch?v=fsnjtv11axk</v>
       </c>
     </row>
     <row r="277">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -13393,11 +13393,14 @@
       <c r="C763" t="str">
         <v>Tecnologia e Cotidiano</v>
       </c>
-      <c r="D763" t="b">
-        <v>0</v>
+      <c r="D763" t="str">
+        <v>publicado</v>
       </c>
       <c r="E763" t="str">
-        <v/>
+        <v>18/07/2026</v>
+      </c>
+      <c r="F763" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=A_y6MqAdOlQ | Short: https://www.youtube.com/watch?v=CYmdHObf-LE</v>
       </c>
     </row>
     <row r="764">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -1942,11 +1942,14 @@
       <c r="C91" t="str">
         <v>Saúde</v>
       </c>
-      <c r="D91" t="b">
-        <v>0</v>
+      <c r="D91" t="str">
+        <v>publicado</v>
       </c>
       <c r="E91" t="str">
-        <v/>
+        <v>19/07/2026</v>
+      </c>
+      <c r="F91" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=xPGN53tKSA0 | Short: https://www.youtube.com/watch?v=U4oLaPld6zM</v>
       </c>
     </row>
     <row r="92">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -17236,11 +17236,14 @@
       <c r="C988" t="str">
         <v>Profissões e Processos</v>
       </c>
-      <c r="D988" t="b">
-        <v>0</v>
+      <c r="D988" t="str">
+        <v>publicado</v>
       </c>
       <c r="E988" t="str">
-        <v/>
+        <v>20/07/2026</v>
+      </c>
+      <c r="F988" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=mEMim08Y8IQ | Short: https://www.youtube.com/watch?v=-TWcY5AJQ4o</v>
       </c>
     </row>
     <row r="989">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -20461,11 +20461,14 @@
       <c r="C1177" t="str">
         <v>Animais Específicos</v>
       </c>
-      <c r="D1177" t="b">
-        <v>0</v>
+      <c r="D1177" t="str">
+        <v>publicado</v>
       </c>
       <c r="E1177" t="str">
-        <v/>
+        <v>21/07/2026</v>
+      </c>
+      <c r="F1177" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=7mK57G_3_Pk | Short: https://www.youtube.com/watch?v=YUnaWuCVHK0</v>
       </c>
     </row>
     <row r="1178">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -10786,11 +10786,14 @@
       <c r="C610" t="str">
         <v>Curiosidades Científicas</v>
       </c>
-      <c r="D610" t="b">
-        <v>0</v>
+      <c r="D610" t="str">
+        <v>publicado</v>
       </c>
       <c r="E610" t="str">
-        <v/>
+        <v>22/07/2026</v>
+      </c>
+      <c r="F610" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=OvFI6t7KocY | Short: https://www.youtube.com/watch?v=GWUu7rgoWfA</v>
       </c>
     </row>
     <row r="611">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -6207,11 +6207,14 @@
       <c r="C341" t="str">
         <v>Psicologia</v>
       </c>
-      <c r="D341" t="b">
-        <v>0</v>
+      <c r="D341" t="str">
+        <v>publicado</v>
       </c>
       <c r="E341" t="str">
-        <v/>
+        <v>24/07/2026</v>
+      </c>
+      <c r="F341" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=DyEuFIy5VcY | Short: https://www.youtube.com/watch?v=BDsX0gNNB-o</v>
       </c>
     </row>
     <row r="342">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -7692,11 +7692,14 @@
       <c r="C428" t="str">
         <v>Geografia</v>
       </c>
-      <c r="D428" t="b">
-        <v>0</v>
+      <c r="D428" t="str">
+        <v>publicado</v>
       </c>
       <c r="E428" t="str">
-        <v/>
+        <v>25/07/2026</v>
+      </c>
+      <c r="F428" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=jWprLIkGz_g | Short: https://www.youtube.com/watch?v=Ec7lAePz24s</v>
       </c>
     </row>
     <row r="429">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -19427,11 +19427,14 @@
       <c r="C1116" t="str">
         <v>Países e Culturas</v>
       </c>
-      <c r="D1116" t="b">
-        <v>0</v>
+      <c r="D1116" t="str">
+        <v>publicado</v>
       </c>
       <c r="E1116" t="str">
-        <v/>
+        <v>26/07/2026</v>
+      </c>
+      <c r="F1116" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=xBVR_naiymI | Short: https://www.youtube.com/watch?v=zEi3zphCh5I</v>
       </c>
     </row>
     <row r="1117">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -6550,11 +6550,14 @@
       <c r="C361" t="str">
         <v>História</v>
       </c>
-      <c r="D361" t="b">
-        <v>0</v>
+      <c r="D361" t="str">
+        <v>publicado</v>
       </c>
       <c r="E361" t="str">
-        <v/>
+        <v>27/07/2026</v>
+      </c>
+      <c r="F361" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=Xsi_mzd1_AY | Short: https://www.youtube.com/watch?v=FNjxfS9zTyc</v>
       </c>
     </row>
     <row r="362">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -17727,11 +17727,14 @@
       <c r="C1016" t="str">
         <v>Países e Culturas</v>
       </c>
-      <c r="D1016" t="b">
-        <v>0</v>
+      <c r="D1016" t="str">
+        <v>publicado</v>
       </c>
       <c r="E1016" t="str">
-        <v/>
+        <v>29/07/2026</v>
+      </c>
+      <c r="F1016" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=TYHkP4rKJ0s | Short: https://www.youtube.com/watch?v=b4EnDFNfb8U</v>
       </c>
     </row>
     <row r="1017">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -1925,11 +1925,14 @@
       <c r="C90" t="str">
         <v>Saúde</v>
       </c>
-      <c r="D90" t="b">
-        <v>0</v>
+      <c r="D90" t="str">
+        <v>publicado</v>
       </c>
       <c r="E90" t="str">
-        <v/>
+        <v>30/07/2026</v>
+      </c>
+      <c r="F90" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=NrHksFAyVCU | Short: https://www.youtube.com/watch?v=MbYUrcbpDlA</v>
       </c>
     </row>
     <row r="91">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -20638,11 +20638,14 @@
       <c r="C1186" t="str">
         <v>Animais Específicos</v>
       </c>
-      <c r="D1186" t="b">
-        <v>0</v>
+      <c r="D1186" t="str">
+        <v>publicado</v>
       </c>
       <c r="E1186" t="str">
-        <v/>
+        <v>31/07/2026</v>
+      </c>
+      <c r="F1186" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=tgjWbJI8tMk | Short: https://www.youtube.com/watch?v=T5uC9QcmwkY</v>
       </c>
     </row>
     <row r="1187">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -2016,11 +2016,14 @@
       <c r="C95" t="str">
         <v>Saúde</v>
       </c>
-      <c r="D95" t="b">
-        <v>0</v>
+      <c r="D95" t="str">
+        <v>publicado</v>
       </c>
       <c r="E95" t="str">
-        <v/>
+        <v>01/08/2026</v>
+      </c>
+      <c r="F95" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=uwLWL1C34F8 | Short: https://www.youtube.com/watch?v=Zn37w5HsiZE</v>
       </c>
     </row>
     <row r="96">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -14913,11 +14913,14 @@
       <c r="C851" t="str">
         <v>Profissões e Processos</v>
       </c>
-      <c r="D851" t="b">
-        <v>0</v>
+      <c r="D851" t="str">
+        <v>publicado</v>
       </c>
       <c r="E851" t="str">
-        <v/>
+        <v>02/08/2026</v>
+      </c>
+      <c r="F851" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=6gEyskTNvIQ | Short: https://www.youtube.com/watch?v=RqyfRGMkjzs</v>
       </c>
     </row>
     <row r="852">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -11810,11 +11810,14 @@
       <c r="C669" t="str">
         <v>Tecnologia e Cotidiano</v>
       </c>
-      <c r="D669" t="b">
-        <v>0</v>
+      <c r="D669" t="str">
+        <v>publicado</v>
       </c>
       <c r="E669" t="str">
-        <v/>
+        <v>03/08/2026</v>
+      </c>
+      <c r="F669" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=rME0AZIPqJE | Short: https://www.youtube.com/watch?v=0Ie7YS06488</v>
       </c>
     </row>
     <row r="670">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -13658,11 +13658,14 @@
       <c r="C777" t="str">
         <v>Comparações e Diferenças</v>
       </c>
-      <c r="D777" t="b">
-        <v>0</v>
+      <c r="D777" t="str">
+        <v>publicado</v>
       </c>
       <c r="E777" t="str">
-        <v/>
+        <v>04/08/2026</v>
+      </c>
+      <c r="F777" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=SiKdRoHsW04 | Short: https://www.youtube.com/watch?v=uIV9hqb9zuw</v>
       </c>
     </row>
     <row r="778">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -11569,11 +11569,14 @@
       <c r="C655" t="str">
         <v>Tecnologia e Cotidiano</v>
       </c>
-      <c r="D655" t="b">
-        <v>0</v>
+      <c r="D655" t="str">
+        <v>publicado</v>
       </c>
       <c r="E655" t="str">
-        <v/>
+        <v>05/08/2026</v>
+      </c>
+      <c r="F655" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=MXgiQ8uAuDw | Short: https://www.youtube.com/watch?v=7VWzh-C0yKY</v>
       </c>
     </row>
     <row r="656">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -14854,11 +14854,14 @@
       <c r="C847" t="str">
         <v>Curiosidades Numéricas</v>
       </c>
-      <c r="D847" t="b">
-        <v>0</v>
+      <c r="D847" t="str">
+        <v>publicado</v>
       </c>
       <c r="E847" t="str">
-        <v/>
+        <v>07/08/2026</v>
+      </c>
+      <c r="F847" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=z8YkuP39V0o | Short: https://www.youtube.com/watch?v=6zj7bpvrEic</v>
       </c>
     </row>
     <row r="848">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -20021,11 +20021,14 @@
       <c r="C1149" t="str">
         <v>Países e Culturas</v>
       </c>
-      <c r="D1149" t="b">
-        <v>0</v>
+      <c r="D1149" t="str">
+        <v>publicado</v>
       </c>
       <c r="E1149" t="str">
-        <v/>
+        <v>08/08/2026</v>
+      </c>
+      <c r="F1149" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=xvHdkuAxXUk | Short: https://www.youtube.com/watch?v=YklsBEFk0qE</v>
       </c>
     </row>
     <row r="1150">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -2427,11 +2427,14 @@
       <c r="C119" t="str">
         <v>Tecnologia</v>
       </c>
-      <c r="D119" t="b">
-        <v>0</v>
+      <c r="D119" t="str">
+        <v>publicado</v>
       </c>
       <c r="E119" t="str">
-        <v/>
+        <v>09/08/2026</v>
+      </c>
+      <c r="F119" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=vtaKNRJXjW8 | Short: https://www.youtube.com/watch?v=rYuTl6jxPig</v>
       </c>
     </row>
     <row r="120">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -13494,11 +13494,14 @@
       <c r="C767" t="str">
         <v>Tecnologia e Cotidiano</v>
       </c>
-      <c r="D767" t="b">
-        <v>0</v>
+      <c r="D767" t="str">
+        <v>publicado</v>
       </c>
       <c r="E767" t="str">
-        <v/>
+        <v>10/08/2026</v>
+      </c>
+      <c r="F767" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=6Vdw5spJUlk | Short: https://www.youtube.com/watch?v=CRa1SgKuWPY</v>
       </c>
     </row>
     <row r="768">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -23312,11 +23312,14 @@
       <c r="C1341" t="str">
         <v>Máquinas e Mecânica</v>
       </c>
-      <c r="D1341" t="b">
-        <v>0</v>
+      <c r="D1341" t="str">
+        <v>publicado</v>
       </c>
       <c r="E1341" t="str">
-        <v/>
+        <v>11/08/2026</v>
+      </c>
+      <c r="F1341" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=oXnYqQDrkgg | Short: https://www.youtube.com/watch?v=gpO1lXSquNA</v>
       </c>
     </row>
     <row r="1342">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -23295,11 +23295,14 @@
       <c r="C1340" t="str">
         <v>Máquinas e Mecânica</v>
       </c>
-      <c r="D1340" t="b">
-        <v>0</v>
+      <c r="D1340" t="str">
+        <v>publicado</v>
       </c>
       <c r="E1340" t="str">
-        <v/>
+        <v>12/08/2026</v>
+      </c>
+      <c r="F1340" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=W4fEjPQUNGg | Short: https://www.youtube.com/watch?v=6I03sfeqK9M</v>
       </c>
     </row>
     <row r="1341">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -23817,11 +23817,14 @@
       <c r="C1370" t="str">
         <v>Máquinas e Mecânica</v>
       </c>
-      <c r="D1370" t="b">
-        <v>0</v>
+      <c r="D1370" t="str">
+        <v>publicado</v>
       </c>
       <c r="E1370" t="str">
-        <v/>
+        <v>13/08/2026</v>
+      </c>
+      <c r="F1370" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=RzfpwQAB21I | Short: https://www.youtube.com/watch?v=DE7Nt1euA9k</v>
       </c>
     </row>
     <row r="1371">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -1823,11 +1823,14 @@
       <c r="C84" t="str">
         <v>Saúde</v>
       </c>
-      <c r="D84" t="b">
-        <v>0</v>
+      <c r="D84" t="str">
+        <v>publicado</v>
       </c>
       <c r="E84" t="str">
-        <v/>
+        <v>14/08/2026</v>
+      </c>
+      <c r="F84" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=j469kxSJdQk | Short: https://www.youtube.com/watch?v=xM1JjpZJo4s</v>
       </c>
     </row>
     <row r="85">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -9070,11 +9070,14 @@
       <c r="C508" t="str">
         <v>Corpo Humano</v>
       </c>
-      <c r="D508" t="b">
-        <v>0</v>
+      <c r="D508" t="str">
+        <v>publicado</v>
       </c>
       <c r="E508" t="str">
-        <v/>
+        <v>15/08/2026</v>
+      </c>
+      <c r="F508" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=9WBUdfaO-a0 | Short: https://www.youtube.com/watch?v=B7SGb-r8rQM</v>
       </c>
     </row>
     <row r="509">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -11944,11 +11944,14 @@
       <c r="C676" t="str">
         <v>Tecnologia e Cotidiano</v>
       </c>
-      <c r="D676" t="b">
-        <v>0</v>
+      <c r="D676" t="str">
+        <v>publicado</v>
       </c>
       <c r="E676" t="str">
-        <v/>
+        <v>16/08/2026</v>
+      </c>
+      <c r="F676" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=CiCbSxbdQQM | Short: https://www.youtube.com/watch?v=cz04LKoVOWc</v>
       </c>
     </row>
     <row r="677">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -16723,11 +16723,14 @@
       <c r="C955" t="str">
         <v>Profissões e Processos</v>
       </c>
-      <c r="D955" t="b">
-        <v>0</v>
+      <c r="D955" t="str">
+        <v>publicado</v>
       </c>
       <c r="E955" t="str">
-        <v/>
+        <v>17/08/2026</v>
+      </c>
+      <c r="F955" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=N8rYwimvdxs | Short: https://www.youtube.com/watch?v=yrq1ocmIfxE</v>
       </c>
     </row>
     <row r="956">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -4601,11 +4601,14 @@
       <c r="C246" t="str">
         <v>Astronomia</v>
       </c>
-      <c r="D246" t="b">
-        <v>0</v>
+      <c r="D246" t="str">
+        <v>publicado</v>
       </c>
       <c r="E246" t="str">
-        <v/>
+        <v>18/08/2026</v>
+      </c>
+      <c r="F246" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=qSKIYz_mcJE | Short: https://www.youtube.com/watch?v=b-jhI0CQDfo</v>
       </c>
     </row>
     <row r="247">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -11740,11 +11740,14 @@
       <c r="C664" t="str">
         <v>Tecnologia e Cotidiano</v>
       </c>
-      <c r="D664" t="b">
-        <v>0</v>
+      <c r="D664" t="str">
+        <v>publicado</v>
       </c>
       <c r="E664" t="str">
-        <v/>
+        <v>20/08/2026</v>
+      </c>
+      <c r="F664" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=fUqkFE4o0eA | Short: https://www.youtube.com/watch?v=y9jMCWjc9oQ</v>
       </c>
     </row>
     <row r="665">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -19532,11 +19532,14 @@
       <c r="C1119" t="str">
         <v>Países e Culturas</v>
       </c>
-      <c r="D1119" t="b">
-        <v>0</v>
+      <c r="D1119" t="str">
+        <v>publicado</v>
       </c>
       <c r="E1119" t="str">
-        <v/>
+        <v>21/08/2026</v>
+      </c>
+      <c r="F1119" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=lPt7qrctSBI | Short: https://www.youtube.com/watch?v=IZfRbxpUpZE</v>
       </c>
     </row>
     <row r="1120">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -8155,11 +8155,14 @@
       <c r="C454" t="str">
         <v>Esportes</v>
       </c>
-      <c r="D454" t="b">
-        <v>0</v>
+      <c r="D454" t="str">
+        <v>publicado</v>
       </c>
       <c r="E454" t="str">
-        <v/>
+        <v>22/08/2026</v>
+      </c>
+      <c r="F454" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=dk68hBk697M | Short: https://www.youtube.com/watch?v=4-qf2lVYPyA</v>
       </c>
     </row>
     <row r="455">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -19002,11 +19002,14 @@
       <c r="C1088" t="str">
         <v>Países e Culturas</v>
       </c>
-      <c r="D1088" t="b">
-        <v>0</v>
+      <c r="D1088" t="str">
+        <v>publicado</v>
       </c>
       <c r="E1088" t="str">
-        <v/>
+        <v>05/09/2026</v>
+      </c>
+      <c r="F1088" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=lDcY0-2sadI | Short: https://www.youtube.com/watch?v=O96e6sxfty8</v>
       </c>
     </row>
     <row r="1089">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -3337,11 +3337,14 @@
       <c r="C172" t="str">
         <v>Curiosidades</v>
       </c>
-      <c r="D172" t="b">
-        <v>0</v>
+      <c r="D172" t="str">
+        <v>publicado</v>
       </c>
       <c r="E172" t="str">
-        <v/>
+        <v>06/09/2026</v>
+      </c>
+      <c r="F172" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=EoIXGdJoSGA | Short: https://www.youtube.com/watch?v=pGyWXA6oqTM</v>
       </c>
     </row>
     <row r="173">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -20094,11 +20094,14 @@
       <c r="C1151" t="str">
         <v>Animais Específicos</v>
       </c>
-      <c r="D1151" t="b">
-        <v>0</v>
+      <c r="D1151" t="str">
+        <v>publicado</v>
       </c>
       <c r="E1151" t="str">
-        <v/>
+        <v>07/09/2026</v>
+      </c>
+      <c r="F1151" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=DNtMqMTmW6c | Short: https://www.youtube.com/watch?v=ERAFNGvzbCU</v>
       </c>
     </row>
     <row r="1152">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -7869,11 +7869,14 @@
       <c r="C437" t="str">
         <v>Geografia</v>
       </c>
-      <c r="D437" t="b">
-        <v>0</v>
+      <c r="D437" t="str">
+        <v>publicado</v>
       </c>
       <c r="E437" t="str">
-        <v/>
+        <v>08/09/2026</v>
+      </c>
+      <c r="F437" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=_tfA0Be4rl8 | Short: https://www.youtube.com/watch?v=J8JMM1j3rQQ</v>
       </c>
     </row>
     <row r="438">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -23439,11 +23439,14 @@
       <c r="C1346" t="str">
         <v>Máquinas e Mecânica</v>
       </c>
-      <c r="D1346" t="b">
-        <v>0</v>
+      <c r="D1346" t="str">
+        <v>publicado</v>
       </c>
       <c r="E1346" t="str">
-        <v/>
+        <v>09/09/2026</v>
+      </c>
+      <c r="F1346" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=r6kPBdR7-cY | Short: https://www.youtube.com/watch?v=aYKFXliu0GQ</v>
       </c>
     </row>
     <row r="1347">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -11097,11 +11097,14 @@
       <c r="C626" t="str">
         <v>Tecnologia e Cotidiano</v>
       </c>
-      <c r="D626" t="b">
-        <v>0</v>
+      <c r="D626" t="str">
+        <v>publicado</v>
       </c>
       <c r="E626" t="str">
-        <v/>
+        <v>10/09/2026</v>
+      </c>
+      <c r="F626" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=ZuTOJVIEWa8 | Short: https://www.youtube.com/watch?v=LCwnoYPpRQs</v>
       </c>
     </row>
     <row r="627">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -22787,11 +22787,14 @@
       <c r="C1308" t="str">
         <v>Máquinas e Mecânica</v>
       </c>
-      <c r="D1308" t="b">
-        <v>0</v>
+      <c r="D1308" t="str">
+        <v>publicado</v>
       </c>
       <c r="E1308" t="str">
-        <v/>
+        <v>11/09/2026</v>
+      </c>
+      <c r="F1308" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=ZINjOOhQ4Xg | Short: https://www.youtube.com/watch?v=AqrF_DQoPyA</v>
       </c>
     </row>
     <row r="1309">

--- a/temas/temas.xlsx
+++ b/temas/temas.xlsx
@@ -3045,11 +3045,14 @@
       <c r="C155" t="str">
         <v>Curiosidades</v>
       </c>
-      <c r="D155" t="b">
-        <v>0</v>
+      <c r="D155" t="str">
+        <v>publicado</v>
       </c>
       <c r="E155" t="str">
-        <v/>
+        <v>12/09/2026</v>
+      </c>
+      <c r="F155" t="str">
+        <v>Longo: https://www.youtube.com/watch?v=0AcXMLzaUAA | Short: https://www.youtube.com/watch?v=BT3ujyt6oso</v>
       </c>
     </row>
     <row r="156">
